--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260720_210158.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
